--- a/objects/cancer_treatment.xlsx
+++ b/objects/cancer_treatment.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -23,6 +23,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -38,202 +41,256 @@
     <t xml:space="preserve">Chemotherapy</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82 (3.47, 4.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37 (1.98, 2.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65 (3.79, 5.70)</t>
+    <t xml:space="preserve">4.01 (3.68, 4.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83 (3.51, 4.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37 (1.99, 2.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78 (3.94, 5.79)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82 (3.47, 4.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66 (3.79, 5.70)</t>
+    <t xml:space="preserve">3.84 (3.51, 4.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38 (1.99, 2.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79 (3.94, 5.79)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35 (2.12, 2.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42 (1.17, 1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89 (1.52, 2.34)</t>
+    <t xml:space="preserve">2.36 (2.15, 2.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35 (2.13, 2.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42 (1.18, 1.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90 (1.55, 2.32)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49 (2.24, 2.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46 (1.19, 1.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88 (1.49, 2.36)</t>
+    <t xml:space="preserve">2.47 (2.23, 2.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49 (2.25, 2.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46 (1.20, 1.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80 (1.44, 2.23)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41 (2.14, 2.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86 (1.48, 2.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78 (1.38, 2.29)</t>
+    <t xml:space="preserve">2.27 (2.04, 2.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34 (2.10, 2.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83 (1.47, 2.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (1.28, 2.06)</t>
   </si>
   <si>
     <t xml:space="preserve">No treatment/Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10 (0.99, 1.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08 (0.89, 1.31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31 (1.87, 2.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10 (0.98, 1.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09 (0.89, 1.31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32 (1.87, 2.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70 (0.62, 0.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.57, 0.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01 (0.81, 1.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.65, 0.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71 (0.57, 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99 (0.78, 1.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78 (0.68, 0.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92 (0.72, 1.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07 (0.83, 1.39)</t>
+    <t xml:space="preserve">1.28 (1.16, 1.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14 (1.03, 1.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (0.94, 1.35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36 (1.94, 2.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (1.03, 1.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37 (1.94, 2.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78 (0.70, 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73 (0.65, 0.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72 (0.59, 0.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02 (0.83, 1.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81 (0.73, 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.68, 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73 (0.59, 0.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95 (0.76, 1.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83 (0.74, 0.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80 (0.70, 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93 (0.74, 1.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01 (0.79, 1.28)</t>
   </si>
   <si>
     <t xml:space="preserve">Radiation Only</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64 (1.11, 2.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26 (0.59, 2.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98 (2.10, 7.55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66 (1.10, 2.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (0.59, 2.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16 (2.09, 7.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87 (0.57, 1.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (0.29, 1.31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31 (0.65, 2.37)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80 (0.50, 1.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59 (0.22, 1.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11 (0.48, 2.21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93 (0.56, 1.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79 (0.26, 1.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02 (0.38, 2.22)</t>
+    <t xml:space="preserve">1.70 (1.19, 2.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48 (1.00, 2.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20 (0.56, 2.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62 (1.91, 6.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72 (1.19, 2.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50 (1.00, 2.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28 (0.56, 2.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79 (1.90, 6.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84 (0.58, 1.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78 (0.52, 1.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64 (0.28, 1.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18 (0.59, 2.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.49, 1.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70 (0.43, 1.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57 (0.21, 1.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99 (0.43, 1.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80 (0.50, 1.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76 (0.45, 1.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74 (0.25, 1.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86 (0.32, 1.87)</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery Only</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87 (0.50, 1.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42 (0.11, 1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40 (0.45, 4.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90 (0.49, 1.50)</t>
+    <t xml:space="preserve">0.96 (0.58, 1.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90 (0.53, 1.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43 (0.11, 1.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34 (0.43, 4.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99 (0.58, 1.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93 (0.52, 1.53)</t>
   </si>
   <si>
     <t xml:space="preserve">0.53 (0.11, 1.50)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62 (0.45, 4.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47 (0.26, 0.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27 (0.06, 0.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57 (0.16, 1.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47 (0.24, 0.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31 (0.06, 0.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64 (0.18, 1.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58 (0.30, 1.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48 (0.10, 1.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77 (0.21, 1.96)</t>
+    <t xml:space="preserve">1.56 (0.44, 3.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49 (0.29, 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49 (0.27, 0.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28 (0.06, 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55 (0.15, 1.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48 (0.26, 0.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46 (0.24, 0.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32 (0.07, 0.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61 (0.17, 1.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56 (0.30, 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55 (0.29, 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49 (0.10, 1.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71 (0.20, 1.80)</t>
   </si>
 </sst>
 </file>
@@ -578,90 +635,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -691,90 +766,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -804,90 +897,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -917,90 +1028,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>78</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>90</v>
+      </c>
+      <c r="F6" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/objects/cancer_treatment.xlsx
+++ b/objects/cancer_treatment.xlsx
@@ -68,46 +68,46 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36 (2.15, 2.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35 (2.13, 2.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42 (1.18, 1.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90 (1.55, 2.32)</t>
+    <t xml:space="preserve">2.38 (2.17, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37 (2.15, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41 (1.17, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89 (1.54, 2.31)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47 (2.23, 2.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49 (2.25, 2.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46 (1.20, 1.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80 (1.44, 2.23)</t>
+    <t xml:space="preserve">2.49 (2.25, 2.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52 (2.27, 2.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45 (1.19, 1.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79 (1.44, 2.22)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27 (2.04, 2.53)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34 (2.10, 2.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83 (1.47, 2.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63 (1.28, 2.06)</t>
+    <t xml:space="preserve">2.28 (2.05, 2.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36 (2.11, 2.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84 (1.48, 2.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (1.29, 2.06)</t>
   </si>
   <si>
     <t xml:space="preserve">No treatment/Unknown</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.83 (0.74, 0.93)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80 (0.70, 0.90)</t>
+    <t xml:space="preserve">0.79 (0.70, 0.90)</t>
   </si>
   <si>
     <t xml:space="preserve">0.93 (0.74, 1.17)</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">0.84 (0.58, 1.19)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78 (0.52, 1.13)</t>
+    <t xml:space="preserve">0.78 (0.51, 1.13)</t>
   </si>
   <si>
     <t xml:space="preserve">0.64 (0.28, 1.25)</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">1.18 (0.59, 2.12)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77 (0.49, 1.14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70 (0.43, 1.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57 (0.21, 1.23)</t>
+    <t xml:space="preserve">0.76 (0.49, 1.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69 (0.43, 1.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58 (0.22, 1.23)</t>
   </si>
   <si>
     <t xml:space="preserve">0.99 (0.43, 1.95)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80 (0.50, 1.21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76 (0.45, 1.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.25, 1.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86 (0.32, 1.87)</t>
+    <t xml:space="preserve">0.79 (0.49, 1.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75 (0.45, 1.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74 (0.24, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86 (0.32, 1.86)</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery Only</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">1.56 (0.44, 3.88)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49 (0.29, 0.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49 (0.27, 0.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28 (0.06, 0.79)</t>
+    <t xml:space="preserve">0.50 (0.29, 0.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49 (0.28, 0.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28 (0.06, 0.78)</t>
   </si>
   <si>
     <t xml:space="preserve">0.55 (0.15, 1.37)</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">0.56 (0.30, 0.94)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55 (0.29, 0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49 (0.10, 1.42)</t>
+    <t xml:space="preserve">0.55 (0.29, 0.97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50 (0.10, 1.42)</t>
   </si>
   <si>
     <t xml:space="preserve">0.71 (0.20, 1.80)</t>
